--- a/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T15:35:31+00:00</t>
+    <t>2026-06-18T15:51:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T15:51:50+00:00</t>
+    <t>2026-06-19T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T07:40:12+00:00</t>
+    <t>2026-06-19T07:40:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T07:40:10+00:00</t>
+    <t>2026-06-19T09:09:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T09:09:24+00:00</t>
+    <t>2026-06-19T09:55:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
+++ b/main/ig/StructureDefinition-as-bal-mss-cab.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T09:55:31+00:00</t>
+    <t>2026-07-10T14:23:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
